--- a/Result/profitability/2497.xlsx
+++ b/Result/profitability/2497.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5824999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="N2" t="n">
-        <v>26.17375</v>
+        <v>26.3525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>0.46</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>25.75625</v>
+        <v>25.30375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.43</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2837499999999999</v>
+        <v>0.2875</v>
       </c>
       <c r="N4" t="n">
-        <v>24.3425</v>
+        <v>24.525</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04374999999999996</v>
+        <v>0.1612499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>15.66</v>
+        <v>15.405</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.75</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03000000000000005</v>
+        <v>-0.04500000000000003</v>
       </c>
       <c r="N6" t="n">
-        <v>6.70125</v>
+        <v>6.862500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.42</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1950000000000001</v>
+        <v>-0.205</v>
       </c>
       <c r="N7" t="n">
-        <v>3.691249999999999</v>
+        <v>3.69875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3087500000000001</v>
+        <v>-0.3112500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>3.357499999999999</v>
+        <v>3.29875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.4400000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>1.864999999999999</v>
+        <v>1.865</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1645,10 +1645,10 @@
         <v>-0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4150000000000001</v>
+        <v>-0.415</v>
       </c>
       <c r="N10" t="n">
-        <v>1.507499999999999</v>
+        <v>1.5075</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>-0.365</v>
       </c>
       <c r="N11" t="n">
-        <v>2.633749999999998</v>
+        <v>2.633749999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>-0.2875</v>
       </c>
       <c r="N12" t="n">
-        <v>4.648749999999998</v>
+        <v>4.64875</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2497</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1444</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1072</v>
+      </c>
+      <c r="E75" t="n">
+        <v>373</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="G75" t="n">
+        <v>132</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.12%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>139</v>
+      </c>
+      <c r="K75" t="n">
+        <v>103</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.05625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.02500000000000002</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4699999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0178775199695701</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.875</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.039999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.07322325915290739</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
